--- a/Manual_Testing/UserStory_TestScenarios_ContactModule.xlsx
+++ b/Manual_Testing/UserStory_TestScenarios_ContactModule.xlsx
@@ -14,14 +14,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="qJvgu2OQMZpgVqGI/Ghuj2izEQG5T+xzvK0A0R4Mjck="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="OZP7ClEFIB4rs5S0RkA0xVHRuBFYaNb9WV960qqbwng="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="359">
   <si>
     <t>Issue Type</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Story 1</t>
   </si>
   <si>
-    <t>View Contacts</t>
+    <t>User should be able to view the list of contacts based on access level and open individual contact records to see detailed information.</t>
   </si>
   <si>
     <t>Sub story 1</t>
@@ -68,7 +68,7 @@
     <t>Story 2</t>
   </si>
   <si>
-    <t>Create Contact</t>
+    <t>User should be able to create a new contact by entering required details, with proper validation, and save it successfully in the system.</t>
   </si>
   <si>
     <t>User should be able to create a new contact</t>
@@ -83,7 +83,7 @@
     <t>Story 3</t>
   </si>
   <si>
-    <t>Edit Contacts</t>
+    <t>User should be able to update existing contact details with proper validation and see the changes reflected correctly.</t>
   </si>
   <si>
     <t>Medium</t>
@@ -101,7 +101,7 @@
     <t>Story 4</t>
   </si>
   <si>
-    <t>Delete contact</t>
+    <t>User should be able to delete a contact with a confirmation prompt and ensure it is removed from the contact list.</t>
   </si>
   <si>
     <t>User should be able to delete a contact</t>
@@ -116,7 +116,7 @@
     <t>Story 5</t>
   </si>
   <si>
-    <t>Search and navigate contacts</t>
+    <t>User should be able to search contacts using key details and easily navigate through the contact list and results.</t>
   </si>
   <si>
     <t>User Should search by name/email</t>
@@ -284,18 +284,6 @@
     <t>REQ_Contacts_11</t>
   </si>
   <si>
-    <t>Verify delete confirmation message is displayed</t>
-  </si>
-  <si>
-    <t>1. Click delete and verify confirmation popup</t>
-  </si>
-  <si>
-    <t>TS_Contacts_12</t>
-  </si>
-  <si>
-    <t>REQ_Contacts_12</t>
-  </si>
-  <si>
     <t>Verify deleted contact is removed from contacts list</t>
   </si>
   <si>
@@ -303,10 +291,10 @@
 2. Verify it is no longer visible</t>
   </si>
   <si>
-    <t>TS_Contacts_13</t>
-  </si>
-  <si>
-    <t>REQ_Contacts_13</t>
+    <t>TS_Contacts_12</t>
+  </si>
+  <si>
+    <t>REQ_Contacts_12</t>
   </si>
   <si>
     <t>Verify search functionality using name or email</t>
@@ -317,10 +305,10 @@
 3. Validate no result scenario</t>
   </si>
   <si>
-    <t>TS_Contacts_14</t>
-  </si>
-  <si>
-    <t>REQ_Contacts_14</t>
+    <t>TS_Contacts_13</t>
+  </si>
+  <si>
+    <t>REQ_Contacts_13</t>
   </si>
   <si>
     <t>Verify filter functionality using category and status</t>
@@ -330,10 +318,10 @@
 2. Verify filtered results</t>
   </si>
   <si>
-    <t>TS_Contacts_15</t>
-  </si>
-  <si>
-    <t>REQ_Contacts_15</t>
+    <t>TS_Contacts_14</t>
+  </si>
+  <si>
+    <t>REQ_Contacts_14</t>
   </si>
   <si>
     <t>Verify system behavior for duplicate contact creation</t>
@@ -343,10 +331,10 @@
 2. Validate system response</t>
   </si>
   <si>
-    <t>TS_Contacts_16</t>
-  </si>
-  <si>
-    <t>REQ_Contacts_16</t>
+    <t>TS_Contacts_15</t>
+  </si>
+  <si>
+    <t>REQ_Contacts_15</t>
   </si>
   <si>
     <t>Verify email field validation with invalid format</t>
@@ -445,7 +433,7 @@
     <r>
       <rPr>
         <rFont val="Candara"/>
-        <color rgb="FF0000FF"/>
+        <color rgb="FF7F6000"/>
         <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve">&lt;This cell describes </t>
@@ -454,7 +442,7 @@
       <rPr>
         <rFont val="Candara"/>
         <b/>
-        <color rgb="FF0000FF"/>
+        <color rgb="FF7F6000"/>
         <sz val="10.0"/>
       </rPr>
       <t>what</t>
@@ -462,7 +450,7 @@
     <r>
       <rPr>
         <rFont val="Candara"/>
-        <color rgb="FF0000FF"/>
+        <color rgb="FF7F6000"/>
         <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve"> to test for i.e. the condition which is being tested for&gt;</t>
@@ -472,7 +460,7 @@
     <r>
       <rPr>
         <rFont val="Candara"/>
-        <color rgb="FF0000FF"/>
+        <color rgb="FF7F6000"/>
         <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve">&lt;This cell describes </t>
@@ -481,7 +469,7 @@
       <rPr>
         <rFont val="Candara"/>
         <b/>
-        <color rgb="FF0000FF"/>
+        <color rgb="FF7F6000"/>
         <sz val="10.0"/>
       </rPr>
       <t>how</t>
@@ -489,7 +477,7 @@
     <r>
       <rPr>
         <rFont val="Candara"/>
-        <color rgb="FF0000FF"/>
+        <color rgb="FF7F6000"/>
         <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve"> to test i.e. the detailed testing procedure&gt;</t>
@@ -514,108 +502,648 @@
     <t>New status of test case after it failed in Iteration 1.</t>
   </si>
   <si>
-    <t>TC_Website_01</t>
-  </si>
-  <si>
-    <t>TS_Website_01</t>
-  </si>
-  <si>
-    <t>1.User is able to open the browser and enter the website URL</t>
-  </si>
-  <si>
-    <t>To validate that when website url is entered in the browser it opens the website.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Browser
-2. Enter URL for the website
-</t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.in/</t>
-  </si>
-  <si>
-    <t>It should open the landing page of website</t>
-  </si>
-  <si>
-    <t>On entering the website URL, it opens the landing page.</t>
+    <t>TC_Contacts_01</t>
+  </si>
+  <si>
+    <t>User is logged in to FreeCRM (ui.freecrm.com)</t>
+  </si>
+  <si>
+    <t>validate that the contacts list is displayed on the contacts page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1. Click on Contacts module from the navigation menu
+2. Observe the contacts page</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Contacts list should be displayed on the contacts page</t>
+  </si>
+  <si>
+    <t>The contact list is displayed on the contacts page</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>TC_Contacts_02</t>
+  </si>
+  <si>
+    <t>validate that contacts list loads with all existing contacts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1. Navigate to Contacts page
+2. Verify all contacts are listed</t>
+  </si>
+  <si>
+    <t>All saved contacts should appear in the list</t>
+  </si>
+  <si>
+    <t>All the contacts are present</t>
+  </si>
+  <si>
+    <t>TC_Contacts_03</t>
+  </si>
+  <si>
+    <t>validate that a public contact is visible to all users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1. Create a new contact and set visibility to Public
+2. Login with a different user account
+3. Navigate to Contacts and check visibility</t>
+  </si>
+  <si>
+    <t>Contact Name: Test Public Contact</t>
+  </si>
+  <si>
+    <t>Visibility: Public</t>
+  </si>
+  <si>
+    <t>Public contacts are visible to all</t>
+  </si>
+  <si>
+    <t>TC_Contacts_04</t>
+  </si>
+  <si>
+    <t>validate that a private contact is only visible to the creator</t>
+  </si>
+  <si>
+    <t>1. Create a new contact and set visibility to Private
+2. Login with a different user account
+3. Navigate to Contacts and check visibility</t>
+  </si>
+  <si>
+    <t>Contact Name: Test Private Contact</t>
+  </si>
+  <si>
+    <t>Visibility: Private	Private contact should NOT be visible to other users</t>
+  </si>
+  <si>
+    <t>Private contacts are not visible to user who don't have access</t>
+  </si>
+  <si>
+    <t>TC_Contacts_05</t>
+  </si>
+  <si>
+    <t>validate contacts visibility toggle between Public and Private</t>
+  </si>
+  <si>
+    <t>1. Open an existing contact
+2. Change visibility from Public to Private
+3. Verify visibility change is saved</t>
+  </si>
+  <si>
+    <t>Existing Contact with Public visibility</t>
+  </si>
+  <si>
+    <t>Visibility should update and reflect correctly</t>
+  </si>
+  <si>
+    <t>After the update  everyone is able to see the Changes and private contacts are also visible</t>
+  </si>
+  <si>
+    <t>TC_Contacts_06</t>
+  </si>
+  <si>
+    <t>validate that clicking on a contact opens the contact details page</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page 
+2. Click on any contact name</t>
+  </si>
+  <si>
+    <t>Any existing contact</t>
+  </si>
+  <si>
+    <t>Contact details page should open with full information</t>
+  </si>
+  <si>
+    <t>Yes the details page open successfully</t>
+  </si>
+  <si>
+    <t>TC_Contacts_07</t>
+  </si>
+  <si>
+    <t>validate that all fields are displayed correctly on contact details page</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click on a contact
+3. Verify all fields like name, email, phone, company are visible</t>
+  </si>
+  <si>
+    <t>Contact with all fields filled</t>
+  </si>
+  <si>
+    <t>All fields (name, email, phone, company, address, notes) should be displayed correctly</t>
+  </si>
+  <si>
+    <t>All fields are displayed as it is</t>
+  </si>
+  <si>
+    <t>TC_Contacts_08</t>
+  </si>
+  <si>
+    <t>validate that user can create a new contact with all valid mandatory data</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click on Add New Contact button
+3. Fill all mandatory fields
+4. Click Save</t>
+  </si>
+  <si>
+    <t>First Name: Snehashis Last Name: Mandal Email: snehashismandal@test.com</t>
+  </si>
+  <si>
+    <t>New contact should be created and saved successfully</t>
+  </si>
+  <si>
+    <t>New Contact is created successfully</t>
+  </si>
+  <si>
+    <t>TC_Contacts_09</t>
+  </si>
+  <si>
+    <t>validate that user can create a contact with optional fields filled</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click on Add New Contact
+3. Fill mandatory + optional fields (phone, company, address, notes)
+4. Click Save</t>
+  </si>
+  <si>
+    <t>First Name: Snehashis Last Name: Mandal Email: snehashismandal@test.com Phone: 9876543210 Company: ABC Corp</t>
+  </si>
+  <si>
+    <t>Contact should be saved with all optional fields reflected correctly</t>
+  </si>
+  <si>
+    <t>All the fields are reflected correctly</t>
+  </si>
+  <si>
+    <t>TC_Contacts_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS_Contacts_05	</t>
+  </si>
+  <si>
+    <t>validate that system shows error when all mandatory fields are left blank</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click on Add New Contact
+3. Leave all mandatory fields blank
+4. Click Save</t>
+  </si>
+  <si>
+    <t>No data entered	System should show validation error messages for all mandatory fields</t>
+  </si>
+  <si>
+    <t>Error is Shown by the system</t>
+  </si>
+  <si>
+    <t>TC_Contacts_11</t>
+  </si>
+  <si>
+    <t>validate that system shows error when some mandatory fields are partially filled</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click on Add New Contact
+3. Fill only First Name, leave Email blank
+4. Click Save</t>
+  </si>
+  <si>
+    <t>First Name: Snehashis
+Last Name: (blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System should show error message for missing mandatory field </t>
+  </si>
+  <si>
+    <t>TC_Contacts_12</t>
+  </si>
+  <si>
+    <t>validate that error messages are clear and shown next to relevant fields</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click on Add New Contact
+3. Leave mandatory fields empty
+4. Click Save and observe error messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No data entered	Error messages should be clearly visible next to each mandatory field	</t>
+  </si>
+  <si>
+    <t>Error Message is shown</t>
+  </si>
+  <si>
+    <t>TC_Contacts_13</t>
+  </si>
+  <si>
+    <t>validate that newly created contact appears in the contacts list</t>
+  </si>
+  <si>
+    <t>1. Create a new contact with valid data
+2. Click Save
+3. Navigate back to Contacts list
+4. Search for the newly created contact</t>
+  </si>
+  <si>
+    <t>First Name: Snehashis
+Last Name: Mandal
+Email: snehashismandal@test.com</t>
+  </si>
+  <si>
+    <t>Newly created contact should appear in the contacts list</t>
+  </si>
+  <si>
+    <t>TC_Contacts_14</t>
+  </si>
+  <si>
+    <t>validate that saved contact data is accurate in the contacts list</t>
+  </si>
+  <si>
+    <t>1. Create a new contact
+2. Save and navigate to contacts list
+3. Open the contact and verify all saved data</t>
+  </si>
+  <si>
+    <t>All saved data should match exactly what was entered during creation</t>
+  </si>
+  <si>
+    <t>Saved data are accurate</t>
+  </si>
+  <si>
+    <t>TC_Contacts_15</t>
+  </si>
+  <si>
+    <t>User is logged in to FreeCRM (ui.freecrm.com) and at least one contact exists</t>
+  </si>
+  <si>
+    <t>To validate that user can open a contact and edit its details</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click on an existing contact
+3. Click Edit button
+4. Update First Name and Phone
+5. Click Save</t>
+  </si>
+  <si>
+    <t>Updated First Name: Suvam
+Updated Phone: 9999988888</t>
+  </si>
+  <si>
+    <t>Contact details should be updated and saved successfully</t>
+  </si>
+  <si>
+    <t>details and updated and saved successfully</t>
+  </si>
+  <si>
+    <t>TC_Contacts_16</t>
+  </si>
+  <si>
+    <t>To validate that user can save changes after editing a contact</t>
+  </si>
+  <si>
+    <t>1. Open an existing contact
+2. Edit the Email field
+3. Click Save
+4. Reopen the contact</t>
+  </si>
+  <si>
+    <t>Updated Email: updated@test.com</t>
+  </si>
+  <si>
+    <t>Updated email should be saved and visible on reopening the contact</t>
+  </si>
+  <si>
+    <t>Updated email is visible</t>
+  </si>
+  <si>
+    <t>TC_Contacts_17</t>
+  </si>
+  <si>
+    <t>ser is logged in to FreeCRM (ui.freecrm.com) and a contact has been edited</t>
+  </si>
+  <si>
+    <t>To validate that updated contact data is correctly reflected on the contact details page</t>
+  </si>
+  <si>
+    <t>1. Edit an existing contact (change name and email)
+2. Save changes
+3. Open the contact details page
+4. Verify updated values</t>
+  </si>
+  <si>
+    <t>Updated Name: Michael Scott
+Updated Email: michael@test.com</t>
+  </si>
+  <si>
+    <t>Updated values should be visible correctly on the contact details page</t>
+  </si>
+  <si>
+    <t>It is displayed correctly</t>
+  </si>
+  <si>
+    <t>TC_Contacts_18</t>
+  </si>
+  <si>
+    <t>User is logged in to FreeCRM (ui.freecrm.com) and a contact has been edited</t>
+  </si>
+  <si>
+    <t>o validate that updated data is reflected in the contacts list as well</t>
+  </si>
+  <si>
+    <t>1. Edit an existing contact name
+2. Save changes
+3. Go back to contacts list
+4. Verify updated name appears in list</t>
+  </si>
+  <si>
+    <t>Updated Name: Michael Scott</t>
+  </si>
+  <si>
+    <t>Updated contact name should be visible in the contacts list</t>
+  </si>
+  <si>
+    <t>Name has updated and displayed correctly</t>
+  </si>
+  <si>
+    <t>TC_Contacts_19</t>
+  </si>
+  <si>
+    <t>User is logged in to FreeCRM (ui.freecrm.com) and a contact is open in edit mode</t>
+  </si>
+  <si>
+    <t>To validate that system shows error when mandatory field is cleared during edit</t>
+  </si>
+  <si>
+    <t>1. Open an existing contact
+2. Click Edit
+3. Clear the mandatory Email field
+4. Click Save</t>
+  </si>
+  <si>
+    <t>Last Name field: (cleared/blank)</t>
+  </si>
+  <si>
+    <t>System should show validation error and not save the contact</t>
+  </si>
+  <si>
+    <t>The error has been displayed</t>
+  </si>
+  <si>
+    <t>TC_Contacts_20</t>
+  </si>
+  <si>
+    <t>To validate that user can delete a contact using the delete option</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Select an existing contact
+3. Click on Delete icon/button
+4. Confirm deletion</t>
+  </si>
+  <si>
+    <t>Existing Contact: Snehashis Mandal</t>
+  </si>
+  <si>
+    <t>Contact should be deleted successfully</t>
+  </si>
+  <si>
+    <t>Contact is deleted successfully</t>
+  </si>
+  <si>
+    <t>TC_Contacts_21</t>
+  </si>
+  <si>
+    <t>To validate that cancel on delete does NOT delete the contact</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click Delete on a contact
+3. Click Cancel on the confirmation dialog</t>
+  </si>
+  <si>
+    <t>Contact should NOT be deleted and should remain in the contacts list</t>
+  </si>
+  <si>
+    <t>contact remained as it is</t>
+  </si>
+  <si>
+    <t>TC_Contacts_22</t>
+  </si>
+  <si>
+    <t>User is logged in to FreeCRM (ui.freecrm.com) and a contact has been deleted</t>
+  </si>
+  <si>
+    <t>To validate that deleted contact does not appear in the contacts list</t>
+  </si>
+  <si>
+    <t>1. Note the name of an existing contact
+2. Delete that contact and confirm
+3. Navigate to contacts list
+4. Search for the deleted contact</t>
+  </si>
+  <si>
+    <t>Deleted Contact Name: Snehashis Mandal</t>
+  </si>
+  <si>
+    <t>Deleted contact should NOT appear anywhere in the contacts list</t>
+  </si>
+  <si>
+    <t>Contacts List is updated</t>
+  </si>
+  <si>
+    <t>TC_Contacts_23</t>
+  </si>
+  <si>
+    <t>User is logged in to FreeCRM (ui.freecrm.com) and multiple contacts exist</t>
+  </si>
+  <si>
+    <t>To validate that searching by name returns correct results</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Enter a contact's first name in the search bar
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Search Input: Snehashis</t>
+  </si>
+  <si>
+    <t>only contacts with name "Snehashis" should appear in results</t>
+  </si>
+  <si>
+    <t>only that particular contact is displayed</t>
+  </si>
+  <si>
+    <t>TC_Contacts_24</t>
+  </si>
+  <si>
+    <t>To validate that searching by email returns correct results</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Enter a contact's email in the search bar
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Search Input: snehashismandal@test.com</t>
+  </si>
+  <si>
+    <t>Only the contact with that email should appear in results</t>
+  </si>
+  <si>
+    <t>TC_Contacts_25</t>
+  </si>
+  <si>
+    <t>To validate that searching with no matching result shows appropriate message</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Enter a name that does not exist
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Search Input: xyznonexistent123</t>
+  </si>
+  <si>
+    <t>System should show "No records found" or similar message</t>
+  </si>
+  <si>
+    <t>Showed "No records found"</t>
+  </si>
+  <si>
+    <t>TC_Contacts_26</t>
+  </si>
+  <si>
+    <t>To validate that filter by category displays correct contacts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to Contacts page
+2. Apply filter by a specific Category
+3. Observe filtered results       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Filter: Category = "Customer"</t>
+  </si>
+  <si>
+    <t>Only contacts under that category should be displayed</t>
+  </si>
+  <si>
+    <t>contacts under that category is displayed only</t>
+  </si>
+  <si>
+    <t>TC_Contacts_27</t>
+  </si>
+  <si>
+    <t>To validate that filter by status displays correct contacts</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Apply filter by Status
+3. Observe filtered results</t>
+  </si>
+  <si>
+    <t>Filter: Status = "Active"</t>
+  </si>
+  <si>
+    <t>Only contacts with Active status should be displayed</t>
+  </si>
+  <si>
+    <t>contacts with active status is displayed only</t>
+  </si>
+  <si>
+    <t>TC_Contacts_28</t>
+  </si>
+  <si>
+    <t>User is logged in to FreeCRM (ui.freecrm.com) and a contact already exists</t>
+  </si>
+  <si>
+    <t>To validate system behavior when a duplicate contact is created with same email</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click Add New Contact
+3. Enter same details as an existing contact
+4. Click Save</t>
+  </si>
+  <si>
+    <t>First Name: Snehashis
+Last Name: Mandal
+Email: snehashismandal@test.com (already exists)</t>
+  </si>
+  <si>
+    <t>System should either show a duplicate warning or prevent saving the duplicate contact</t>
+  </si>
+  <si>
+    <t>Duplicate contacts is also added no error message shown</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>TC_RebBus_01</t>
-  </si>
-  <si>
-    <t>Verify Login Functionality</t>
-  </si>
-  <si>
-    <t>RedBus application is displayed on chrome browser</t>
-  </si>
-  <si>
-    <t>To validate Login functionality with valid credentials</t>
-  </si>
-  <si>
-    <t>1. click on Account
-2. click on login in
-3. enter mobile number
-4. enter the OPT
-5. click on continue</t>
-  </si>
-  <si>
-    <t>3. 9876765544</t>
-  </si>
-  <si>
-    <t>It should be successful</t>
-  </si>
-  <si>
-    <t>Login is successful</t>
-  </si>
-  <si>
-    <t>TC_RebBus_02</t>
-  </si>
-  <si>
-    <t>To validate Login with invalid credentials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. click on Account
-2. click on login in
-3. enter invalid mobile number
-</t>
-  </si>
-  <si>
-    <t>3. 0989786543</t>
-  </si>
-  <si>
-    <t>It should provide me the error message</t>
-  </si>
-  <si>
-    <t>TC_RedBus_03</t>
-  </si>
-  <si>
-    <t>Search Functionality</t>
-  </si>
-  <si>
-    <t>1. RedBus application is dispalyed
-2. User should be logged in</t>
-  </si>
-  <si>
-    <t>To validate the search functionality with valid data</t>
-  </si>
-  <si>
-    <t>1. click on search field
-2. enter the valid source &amp; destination
-3. select the date
-5. click on search bus</t>
-  </si>
-  <si>
-    <t>2. Delhi &amp; Mumbai
-3. 29 Jan 2026</t>
-  </si>
-  <si>
-    <t>Should open the bus details as per the data</t>
+    <t>System should through an error if anyone tries to add duplicate contacts</t>
+  </si>
+  <si>
+    <t>TC_Contacts_29</t>
+  </si>
+  <si>
+    <t>To validate system behavior when a duplicate contact is created</t>
+  </si>
+  <si>
+    <t>1. Try creating a contact with an email that already exists
+2. Click Save
+3. Observe the system message</t>
+  </si>
+  <si>
+    <t>Duplicate Email: snehashismandal@test.com</t>
+  </si>
+  <si>
+    <t>A clear warning or error message should be displayed to the user</t>
+  </si>
+  <si>
+    <t>Duplicate email is also added no error message shown</t>
+  </si>
+  <si>
+    <t>System should through an error if anyone tries to add duplicate email to different contacts</t>
+  </si>
+  <si>
+    <t>TC_Contacts_30</t>
+  </si>
+  <si>
+    <t>To validate that entering an invalid email format shows an error</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacts page
+2. Click Add New Contact
+3. Enter invalid email in Email field
+4. Click Save</t>
+  </si>
+  <si>
+    <t>Invalid Email: snehashismandal@</t>
+  </si>
+  <si>
+    <t>System should show an error message indicating invalid email format</t>
+  </si>
+  <si>
+    <t>Invalid is not added along with these no error message is displayed</t>
+  </si>
+  <si>
+    <t>System should through an error if the email provided is invalid</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Defect Id.</t>
@@ -636,36 +1164,30 @@
     <t>Status</t>
   </si>
   <si>
-    <t>DF_LandingPage_01</t>
-  </si>
-  <si>
-    <t>Landing Page</t>
-  </si>
-  <si>
-    <t>Sign Up (Create Account)option is not available on landing page.</t>
-  </si>
-  <si>
-    <t>abc@capgemini.com</t>
-  </si>
-  <si>
-    <t>To do</t>
-  </si>
-  <si>
-    <t>DF_RedBus_01</t>
-  </si>
-  <si>
-    <t>Login functionality</t>
-  </si>
-  <si>
-    <t>invalid data can be accepted in login</t>
-  </si>
-  <si>
-    <t>deepa@gmail.com</t>
+    <t>DF_Contacts_01</t>
+  </si>
+  <si>
+    <t>Contacts Management</t>
+  </si>
+  <si>
+    <t>System allows creation of duplicate contacts with same  name and email without showing any warning or error message</t>
   </si>
   <si>
     <t>New</t>
   </si>
   <si>
+    <t>DF_Contacts_02</t>
+  </si>
+  <si>
+    <t>System allows duplicate email address to be saved for different contacts without displaying any error oe warning message</t>
+  </si>
+  <si>
+    <t>DF_Contacts_03</t>
+  </si>
+  <si>
+    <t>System does show any warning or error for invalid email but after saving the invalid email it is not updated it is blank there in th email section</t>
+  </si>
+  <si>
     <t>BR_ID</t>
   </si>
   <si>
@@ -684,58 +1206,52 @@
     <t>DR_ID</t>
   </si>
   <si>
-    <t>BR_Website_01</t>
-  </si>
-  <si>
-    <t>TR_Website_01</t>
+    <t>TR_Contacts_01</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>TC_Website_02</t>
-  </si>
-  <si>
-    <t>TC_Website_03</t>
-  </si>
-  <si>
-    <t>BR_RedBus_01</t>
-  </si>
-  <si>
-    <t>TR_RedBus_01</t>
-  </si>
-  <si>
-    <t>TS_RedBus_01</t>
-  </si>
-  <si>
-    <t>TC_RedBus_01</t>
-  </si>
-  <si>
-    <t>TC_RedBus_02</t>
-  </si>
-  <si>
-    <t>TC_RedBus_04</t>
-  </si>
-  <si>
-    <t>BR_RedBus_02</t>
-  </si>
-  <si>
-    <t>TR_RedBus_02</t>
-  </si>
-  <si>
-    <t>TS_RedBus_02</t>
-  </si>
-  <si>
-    <t>TC_RedBus_05</t>
-  </si>
-  <si>
-    <t>TC_RedBus_06</t>
-  </si>
-  <si>
-    <t>TC_RedBus+07</t>
-  </si>
-  <si>
-    <t>TC_RedBus_08</t>
+    <t>TR_Contacts_02</t>
+  </si>
+  <si>
+    <t>TR_Contacts_03</t>
+  </si>
+  <si>
+    <t>TR_Contacts_04</t>
+  </si>
+  <si>
+    <t>TR_Contacts_05</t>
+  </si>
+  <si>
+    <t>TR_Contacts_06</t>
+  </si>
+  <si>
+    <t>TR_Contacts_07</t>
+  </si>
+  <si>
+    <t>TR_Contacts_08</t>
+  </si>
+  <si>
+    <t>TR_Contacts_09</t>
+  </si>
+  <si>
+    <t>TR_Contacts_10</t>
+  </si>
+  <si>
+    <t>TR_Contacts_11</t>
+  </si>
+  <si>
+    <t>TR_Contacts_12</t>
+  </si>
+  <si>
+    <t>TR_Contacts_13</t>
+  </si>
+  <si>
+    <t>TR_Contacts_14</t>
+  </si>
+  <si>
+    <t>TR_Contacts_15</t>
   </si>
   <si>
     <t>TEST EXECUTION SUMMARY</t>
@@ -765,23 +1281,17 @@
     <t>Fail Percentage</t>
   </si>
   <si>
-    <t>Complition Percentage</t>
-  </si>
-  <si>
-    <t>Universal  Class</t>
-  </si>
-  <si>
-    <t>Sign In</t>
-  </si>
-  <si>
-    <t>Sign Up</t>
+    <t>Completion Percentage</t>
+  </si>
+  <si>
+    <t>FreeCRM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="17">
+  <fonts count="13">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -838,40 +1348,17 @@
     </font>
     <font>
       <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F6000"/>
       <name val="Candara"/>
     </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Candara"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font/>
     <font>
       <sz val="24.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -922,8 +1409,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4B083"/>
-        <bgColor rgb="FFF4B083"/>
+        <fgColor rgb="FFC9DAF8"/>
+        <bgColor rgb="FFC9DAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
     <fill>
@@ -934,12 +1427,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFF4B083"/>
+        <bgColor rgb="FFF4B083"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93C47D"/>
+        <bgColor rgb="FF93C47D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE06666"/>
+        <bgColor rgb="FFE06666"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border/>
     <border>
       <left style="thin">
@@ -1018,25 +1523,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1067,7 +1553,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="50">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1156,99 +1642,65 @@
     <xf borderId="1" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="13" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="11" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="9" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="11" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="9" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="9" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -3101,7 +3553,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" ht="45.0" customHeight="1">
+    <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="21" t="s">
         <v>81</v>
       </c>
@@ -3115,13 +3567,13 @@
         <v>43</v>
       </c>
       <c r="E12" s="21">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="48.0" customHeight="1">
       <c r="A13" s="21" t="s">
         <v>85</v>
       </c>
@@ -3135,13 +3587,13 @@
         <v>43</v>
       </c>
       <c r="E13" s="21">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" ht="48.0" customHeight="1">
+    <row r="14" ht="34.5" customHeight="1">
       <c r="A14" s="21" t="s">
         <v>89</v>
       </c>
@@ -3155,13 +3607,13 @@
         <v>43</v>
       </c>
       <c r="E14" s="21">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" ht="34.5" customHeight="1">
+    <row r="15" ht="43.5" customHeight="1">
       <c r="A15" s="21" t="s">
         <v>93</v>
       </c>
@@ -3181,7 +3633,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" ht="43.5" customHeight="1">
+    <row r="16" ht="50.25" customHeight="1">
       <c r="A16" s="21" t="s">
         <v>97</v>
       </c>
@@ -3201,1268 +3653,6 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" ht="50.25" customHeight="1">
-      <c r="A17" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-  </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="19.0"/>
-    <col customWidth="1" min="2" max="2" width="16.43"/>
-    <col customWidth="1" min="3" max="3" width="21.71"/>
-    <col customWidth="1" min="4" max="4" width="28.43"/>
-    <col customWidth="1" min="5" max="5" width="17.0"/>
-    <col customWidth="1" min="6" max="6" width="20.0"/>
-    <col customWidth="1" min="7" max="7" width="14.71"/>
-    <col customWidth="1" min="8" max="8" width="19.86"/>
-    <col customWidth="1" min="9" max="9" width="20.14"/>
-    <col customWidth="1" min="10" max="10" width="23.86"/>
-    <col customWidth="1" min="11" max="11" width="16.14"/>
-    <col customWidth="1" min="12" max="12" width="8.71"/>
-    <col customWidth="1" min="13" max="13" width="8.86"/>
-    <col customWidth="1" min="14" max="26" width="8.71"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="87.0" customHeight="1">
-      <c r="A1" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" ht="57.0" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="L2" s="30"/>
-      <c r="M2" s="31"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="I3" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="J3" s="37"/>
-      <c r="K3" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -5441,167 +4631,1086 @@
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
     <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="0" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH(("Hold"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="2" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH(("Passed"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3">
-    <cfRule type="containsText" dxfId="0" priority="4" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH(("Hold"),(K3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3">
-    <cfRule type="cellIs" dxfId="1" priority="5" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3">
-    <cfRule type="containsText" dxfId="2" priority="6" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH(("Passed"),(K3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I3 K3">
-      <formula1>"Passed,Failed,Hold"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="F3"/>
-  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.43"/>
-    <col customWidth="1" min="2" max="2" width="17.86"/>
-    <col customWidth="1" min="3" max="3" width="21.86"/>
-    <col customWidth="1" min="4" max="4" width="21.43"/>
-    <col customWidth="1" min="5" max="5" width="25.0"/>
-    <col customWidth="1" min="6" max="6" width="14.14"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="19.0"/>
+    <col customWidth="1" min="2" max="2" width="16.43"/>
+    <col customWidth="1" min="3" max="3" width="67.86"/>
+    <col customWidth="1" min="4" max="4" width="59.57"/>
+    <col customWidth="1" min="5" max="5" width="58.57"/>
+    <col customWidth="1" min="6" max="6" width="57.43"/>
+    <col customWidth="1" min="7" max="7" width="65.43"/>
+    <col customWidth="1" min="8" max="8" width="46.0"/>
+    <col customWidth="1" min="9" max="9" width="20.14"/>
+    <col customWidth="1" min="10" max="10" width="23.86"/>
+    <col customWidth="1" min="11" max="11" width="16.14"/>
+    <col customWidth="1" min="12" max="12" width="39.43"/>
+    <col customWidth="1" min="13" max="13" width="23.0"/>
+    <col customWidth="1" min="14" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+    <row r="1" ht="87.0" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" ht="57.0" customHeight="1">
+      <c r="A2" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="L2" s="30"/>
+      <c r="M2" s="31"/>
+    </row>
+    <row r="3" ht="81.75" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" ht="60.75" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" ht="64.5" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="G8" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="H8" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="I8" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" ht="66.75" customHeight="1">
+      <c r="A9" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="B9" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="E9" s="21" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="2" ht="69.75" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="F9" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="G9" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="H9" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="41" t="s">
+      <c r="I9" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="B10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="20"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="F10" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="G10" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="42" t="s">
+      <c r="H10" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="I10" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="20"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+      <c r="B11" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="L27" s="35"/>
+      <c r="M27" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="I28" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="M29" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="L30" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="L31" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="I32" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -5609,7 +5718,11 @@
     <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="M40" s="36" t="s">
+        <v>311</v>
+      </c>
+    </row>
     <row r="41" ht="14.25" customHeight="1"/>
     <row r="42" ht="14.25" customHeight="1"/>
     <row r="43" ht="14.25" customHeight="1"/>
@@ -6564,1362 +6677,105 @@
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
     <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="E2"/>
-    <hyperlink r:id="rId2" ref="E4"/>
-  </hyperlinks>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I32">
+      <formula1>"Passed,Failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.86"/>
-    <col customWidth="1" min="3" max="3" width="29.43"/>
-    <col customWidth="1" min="4" max="4" width="34.14"/>
-    <col customWidth="1" min="5" max="5" width="11.43"/>
-    <col customWidth="1" min="6" max="6" width="33.14"/>
+    <col customWidth="1" min="1" max="1" width="17.43"/>
+    <col customWidth="1" min="2" max="2" width="17.86"/>
+    <col customWidth="1" min="3" max="3" width="21.86"/>
+    <col customWidth="1" min="4" max="4" width="21.43"/>
+    <col customWidth="1" min="5" max="5" width="25.0"/>
+    <col customWidth="1" min="6" max="6" width="14.14"/>
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="C1" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="D1" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="F1" s="43" t="s">
-        <v>180</v>
+      <c r="A1" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>183</v>
+      <c r="A2" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="45" t="s">
-        <v>165</v>
+      <c r="A3" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="45"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="F5" s="45" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F8" s="37"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10" s="37"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="37"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="37"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" s="37"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F14" s="37"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E2:E5">
-    <cfRule type="containsText" dxfId="0" priority="1" stopIfTrue="1" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH(("Hold"),(E2))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
-      <formula>"Failed"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
-    <cfRule type="containsText" dxfId="2" priority="3" stopIfTrue="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH(("Passed"),(E2))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E5">
-      <formula1>"Passed,Failed,Hold"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="17.86"/>
-    <col customWidth="1" min="2" max="2" width="19.57"/>
-    <col customWidth="1" min="3" max="3" width="10.14"/>
-    <col customWidth="1" min="4" max="4" width="11.14"/>
-    <col customWidth="1" min="5" max="5" width="10.43"/>
-    <col customWidth="1" min="6" max="6" width="13.14"/>
-    <col customWidth="1" min="7" max="7" width="14.14"/>
-    <col customWidth="1" min="8" max="8" width="13.43"/>
-    <col customWidth="1" min="9" max="9" width="19.71"/>
-    <col customWidth="1" min="10" max="26" width="8.71"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="51"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>205</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="52" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="D3" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="E3" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="G3" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="H3" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="54">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="D4" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="E4" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="G4" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="H4" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="54">
-        <v>1.0</v>
+      <c r="A4" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
@@ -8917,7 +7773,2559 @@
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
     <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.29"/>
+    <col customWidth="1" min="2" max="2" width="15.86"/>
+    <col customWidth="1" min="3" max="3" width="29.43"/>
+    <col customWidth="1" min="4" max="4" width="34.14"/>
+    <col customWidth="1" min="5" max="5" width="11.43"/>
+    <col customWidth="1" min="6" max="6" width="33.14"/>
+    <col customWidth="1" min="7" max="26" width="8.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" customHeight="1">
+      <c r="A1" s="39" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>329</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="D3" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="D5" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="D6" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="D8" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="D10" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="D12" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="D13" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="D15" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="D17" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="D19" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="D22" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="D25" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="D26" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="D28" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="D30" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="17.86"/>
+    <col customWidth="1" min="2" max="2" width="19.57"/>
+    <col customWidth="1" min="3" max="3" width="10.14"/>
+    <col customWidth="1" min="4" max="4" width="11.14"/>
+    <col customWidth="1" min="5" max="5" width="10.43"/>
+    <col customWidth="1" min="6" max="6" width="13.14"/>
+    <col customWidth="1" min="7" max="7" width="14.14"/>
+    <col customWidth="1" min="8" max="8" width="13.43"/>
+    <col customWidth="1" min="9" max="9" width="21.0"/>
+    <col customWidth="1" min="10" max="26" width="8.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="51.75" customHeight="1">
+      <c r="A1" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="44"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="39" t="s">
+        <v>349</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>351</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>352</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>353</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="47">
+        <v>30.0</v>
+      </c>
+      <c r="D3" s="47">
+        <v>27.0</v>
+      </c>
+      <c r="E3" s="47">
+        <v>3.0</v>
+      </c>
+      <c r="F3" s="47">
+        <v>30.0</v>
+      </c>
+      <c r="G3" s="48">
+        <v>0.9</v>
+      </c>
+      <c r="H3" s="48">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="49">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1"/>
+    <row r="5" ht="14.25" customHeight="1"/>
+    <row r="6" ht="14.25" customHeight="1"/>
+    <row r="7" ht="14.25" customHeight="1"/>
+    <row r="8" ht="14.25" customHeight="1"/>
+    <row r="9" ht="14.25" customHeight="1"/>
+    <row r="10" ht="14.25" customHeight="1"/>
+    <row r="11" ht="14.25" customHeight="1"/>
+    <row r="12" ht="14.25" customHeight="1"/>
+    <row r="13" ht="14.25" customHeight="1"/>
+    <row r="14" ht="14.25" customHeight="1"/>
+    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
